--- a/附件包/Vector.xlsx
+++ b/附件包/Vector.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\KratosAI\附件包\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C2A51B-2627-4C4C-8412-C43EC707CF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895DE8D9-E8A7-441E-A8A8-960629A56D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vector 标签" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="333">
   <si>
     <t>标签名 (Vector.xxx)</t>
   </si>
@@ -3676,6 +3676,80 @@
         <family val="2"/>
       </rPr>
       <t>关掉动态圆的高度部分</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>vector</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>控制的东西跑到地面以下后就自动结束</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AE</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.RemoveOnUndergroundTolerance</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.RemoveOnUnderground</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector.SetToGroundHeight</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>跑到地下384</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>lepton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>后才触发。默认384，写负数可以在地表结束</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>如果跑到地面以下就强制钳位到地表</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -3982,7 +4056,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4139,6 +4213,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -4172,22 +4264,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -4495,7 +4572,7 @@
   <dimension ref="A1:D132"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="47.375" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="144" customWidth="1"/>
@@ -4516,12 +4593,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="68"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="76"/>
     </row>
     <row r="3" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
@@ -4656,15 +4733,55 @@
       <c r="B12" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="69" t="s">
         <v>102</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="35" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="13" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A13" s="46" t="s">
+        <v>329</v>
+      </c>
+      <c r="B13" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="71" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="35" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="B14" s="69" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="69">
+        <v>384</v>
+      </c>
+      <c r="D14" s="87" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="B15" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="87" t="s">
+        <v>332</v>
+      </c>
+    </row>
     <row r="16" spans="1:4" s="12" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="55" t="s">
         <v>251</v>
@@ -4918,12 +5035,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="77" t="s">
         <v>248</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="71"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="79"/>
     </row>
     <row r="2" spans="1:4" ht="24" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -4940,12 +5057,12 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="74"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="82"/>
     </row>
     <row r="5" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
@@ -5010,12 +5127,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="83" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="77"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="85"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="16" t="s">
@@ -5102,12 +5219,12 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="86" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="76"/>
-      <c r="C10" s="76"/>
-      <c r="D10" s="77"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="85"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="17" t="s">
@@ -5138,12 +5255,12 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="76"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="77"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="85"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" s="19" t="s">
@@ -5434,12 +5551,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="77"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="85"/>
     </row>
     <row r="2" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -5568,7 +5685,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="79" t="s">
+      <c r="A11" s="66" t="s">
         <v>306</v>
       </c>
       <c r="B11" s="48" t="s">
@@ -5577,12 +5694,12 @@
       <c r="C11" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="80" t="s">
+      <c r="D11" s="67" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="79" t="s">
+      <c r="A12" s="66" t="s">
         <v>307</v>
       </c>
       <c r="B12" s="48" t="s">
@@ -5591,12 +5708,12 @@
       <c r="C12" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="80" t="s">
+      <c r="D12" s="67" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="66" t="s">
         <v>308</v>
       </c>
       <c r="B13" s="48" t="s">
@@ -5605,7 +5722,7 @@
       <c r="C13" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="80" t="s">
+      <c r="D13" s="67" t="s">
         <v>314</v>
       </c>
     </row>
@@ -5792,12 +5909,12 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A32" s="75" t="s">
+      <c r="A32" s="83" t="s">
         <v>118</v>
       </c>
-      <c r="B32" s="76"/>
-      <c r="C32" s="76"/>
-      <c r="D32" s="77"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="85"/>
     </row>
     <row r="33" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
@@ -6580,72 +6697,72 @@
       </c>
     </row>
     <row r="94" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A94" s="83" t="s">
+      <c r="A94" s="70" t="s">
         <v>315</v>
       </c>
-      <c r="B94" s="81" t="s">
+      <c r="B94" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="C94" s="81" t="s">
+      <c r="C94" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="D94" s="84" t="s">
+      <c r="D94" s="71" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A95" s="83" t="s">
+      <c r="A95" s="70" t="s">
         <v>316</v>
       </c>
-      <c r="B95" s="81" t="s">
+      <c r="B95" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="C95" s="81" t="s">
+      <c r="C95" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="D95" s="84" t="s">
+      <c r="D95" s="71" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A96" s="85" t="s">
+      <c r="A96" s="72" t="s">
         <v>317</v>
       </c>
-      <c r="B96" s="82" t="s">
+      <c r="B96" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C96" s="82" t="s">
+      <c r="C96" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D96" s="86" t="s">
+      <c r="D96" s="73" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A97" s="85" t="s">
+      <c r="A97" s="72" t="s">
         <v>318</v>
       </c>
-      <c r="B97" s="82" t="s">
+      <c r="B97" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C97" s="82" t="s">
+      <c r="C97" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D97" s="86" t="s">
+      <c r="D97" s="73" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A98" s="85" t="s">
+      <c r="A98" s="72" t="s">
         <v>319</v>
       </c>
-      <c r="B98" s="82" t="s">
+      <c r="B98" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="C98" s="82" t="s">
+      <c r="C98" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="D98" s="86" t="s">
+      <c r="D98" s="73" t="s">
         <v>322</v>
       </c>
     </row>
